--- a/dados/vou-pra-missa.xlsx
+++ b/dados/vou-pra-missa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b51a6397e977f0d1/Documentos/Vou pra Missa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B45345A16BD1007B450F0D24855F578E8C5ECAEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{365B5B79-9113-4E96-8AB9-72789D6469C1}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_B45345A16BD1007B450F0D24855F578E8C5ECAEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62C0413C-E2CF-46FD-9D7D-C17911D3377A}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leia-me" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="472">
   <si>
     <t>VOU PRA MISSA — planilha de igrejas</t>
   </si>
@@ -1487,6 +1487,15 @@
   </si>
   <si>
     <t>09:00-11:30</t>
+  </si>
+  <si>
+    <t>assets/dsmp-001-fachada</t>
+  </si>
+  <si>
+    <t>assets/dsmp-001-fachada;
+assets/dsmp-001-corredor-central;
+assets/dsmp-001-cupula;
+assets/dsmp-001-piabatismal</t>
   </si>
 </sst>
 </file>
@@ -2163,7 +2172,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>451</v>
       </c>
@@ -2216,8 +2225,12 @@
       <c r="R2" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
+      <c r="S2" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="T2" s="16" t="s">
+        <v>471</v>
+      </c>
       <c r="U2" s="8"/>
       <c r="V2" s="8"/>
       <c r="W2" s="8" t="s">

--- a/dados/vou-pra-missa.xlsx
+++ b/dados/vou-pra-missa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b51a6397e977f0d1/Documentos/Vou pra Missa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_B45345A16BD1007B450F0D24855F578E8C5ECAEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62C0413C-E2CF-46FD-9D7D-C17911D3377A}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_B45345A16BD1007B450F0D24855F578E8C5ECAEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E26972A-3931-4343-8B7A-69FB44D31E88}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1489,13 +1489,13 @@
     <t>09:00-11:30</t>
   </si>
   <si>
-    <t>assets/dsmp-001-fachada</t>
-  </si>
-  <si>
-    <t>assets/dsmp-001-fachada;
-assets/dsmp-001-corredor-central;
-assets/dsmp-001-cupula;
-assets/dsmp-001-piabatismal</t>
+    <t>assets/dsmp-001-fachada.jpg</t>
+  </si>
+  <si>
+    <t>assets/dsmp-001-fachada.jpg;
+assets/dsmp-001-corredor-central.jpg;
+assets/dsmp-001-cupula.jpg;
+assets/dsmp-001-piabatismal.jpg</t>
   </si>
 </sst>
 </file>
@@ -2172,7 +2172,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>451</v>
       </c>

--- a/dados/vou-pra-missa.xlsx
+++ b/dados/vou-pra-missa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b51a6397e977f0d1/Documentos/Vou pra Missa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_B45345A16BD1007B450F0D24855F578E8C5ECAEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E26972A-3931-4343-8B7A-69FB44D31E88}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_B45345A16BD1007B450F0D24855F578E8C5ECAEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16DAED64-1BD6-4867-886F-FC0560F4FFAF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="481">
   <si>
     <t>VOU PRA MISSA — planilha de igrejas</t>
   </si>
@@ -1496,6 +1496,34 @@
 assets/dsmp-001-corredor-central.jpg;
 assets/dsmp-001-cupula.jpg;
 assets/dsmp-001-piabatismal.jpg</t>
+  </si>
+  <si>
+    <t>paroquia_mae</t>
+  </si>
+  <si>
+    <t>Rua Gal. Americano Freire, 375 - Vila Minerva
+Cep: 08440-300 - São Paulo - SP</t>
+  </si>
+  <si>
+    <t>(11) 2554.3100</t>
+  </si>
+  <si>
+    <t>sagradafamiliaguaianases@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/psagradafamiliaguaianases/</t>
+  </si>
+  <si>
+    <t>Pároco: Pe. Ronnie Von Ferreira de Souza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acolhida; apostolado da oração; batismo; caridade; catequese; coroinhas; dizimo; familiar; grupo de oração; juventude; legião de maria; liturgia; Mães que oram pelos filhos; ministros leigos; músicos; patrimônio; pascom; terço dos homens </t>
+  </si>
+  <si>
+    <t>assets/dsmp-002-fachada.jpg</t>
+  </si>
+  <si>
+    <t>assets/dsmp-002-fachada.jpg; assets/dsmp-002-altar.jpg; assets/dsmp-002-altar-2.jpg</t>
   </si>
 </sst>
 </file>
@@ -2066,7 +2094,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y109"/>
+  <dimension ref="A1:Z109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2095,7 +2123,7 @@
     <col min="25" max="25" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
@@ -2171,8 +2199,11 @@
       <c r="Y1" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" ht="90" x14ac:dyDescent="0.25">
+      <c r="Z1" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>451</v>
       </c>
@@ -2241,8 +2272,10 @@
         <v>46310</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
+    <row r="3" spans="1:26" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>451</v>
+      </c>
       <c r="B3" s="7" t="s">
         <v>54</v>
       </c>
@@ -2276,21 +2309,39 @@
       <c r="L3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="9"/>
+      <c r="M3" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>474</v>
+      </c>
       <c r="O3" s="9"/>
-      <c r="P3" s="8"/>
+      <c r="P3" s="15" t="s">
+        <v>475</v>
+      </c>
       <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
+      <c r="R3" s="15" t="s">
+        <v>476</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>480</v>
+      </c>
       <c r="U3" s="8"/>
       <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="10"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W3" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="Y3" s="10">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="7" t="s">
         <v>60</v>
@@ -2339,7 +2390,7 @@
       <c r="X4" s="8"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="7" t="s">
         <v>64</v>
@@ -2388,7 +2439,7 @@
       <c r="X5" s="8"/>
       <c r="Y5" s="10"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="7" t="s">
         <v>68</v>
@@ -2437,7 +2488,7 @@
       <c r="X6" s="8"/>
       <c r="Y6" s="10"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="7" t="s">
         <v>73</v>
@@ -2486,7 +2537,7 @@
       <c r="X7" s="8"/>
       <c r="Y7" s="10"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="7" t="s">
         <v>78</v>
@@ -2535,7 +2586,7 @@
       <c r="X8" s="8"/>
       <c r="Y8" s="10"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="7" t="s">
         <v>82</v>
@@ -2584,7 +2635,7 @@
       <c r="X9" s="8"/>
       <c r="Y9" s="10"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="7" t="s">
         <v>86</v>
@@ -2633,7 +2684,7 @@
       <c r="X10" s="8"/>
       <c r="Y10" s="10"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="7" t="s">
         <v>89</v>
@@ -2682,7 +2733,7 @@
       <c r="X11" s="8"/>
       <c r="Y11" s="10"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="7" t="s">
         <v>93</v>
@@ -2731,7 +2782,7 @@
       <c r="X12" s="8"/>
       <c r="Y12" s="10"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="7" t="s">
         <v>97</v>
@@ -2780,7 +2831,7 @@
       <c r="X13" s="8"/>
       <c r="Y13" s="10"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="7" t="s">
         <v>100</v>
@@ -2829,7 +2880,7 @@
       <c r="X14" s="8"/>
       <c r="Y14" s="10"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="7" t="s">
         <v>103</v>
@@ -2878,7 +2929,7 @@
       <c r="X15" s="8"/>
       <c r="Y15" s="10"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="7" t="s">
         <v>106</v>
@@ -7486,8 +7537,11 @@
   <hyperlinks>
     <hyperlink ref="R2" r:id="rId1" xr:uid="{F89F029E-6A47-4232-8D65-11F6C22D57AF}"/>
     <hyperlink ref="P2" r:id="rId2" xr:uid="{A373665D-37EC-4A0E-A274-E5ABC6515CD5}"/>
+    <hyperlink ref="P3" r:id="rId3" xr:uid="{E4E1A6D6-64D9-4C3A-85FC-96189B66F6FF}"/>
+    <hyperlink ref="R3" r:id="rId4" xr:uid="{ED1C82B0-DCFB-43D8-9F0B-2C4A5535B46F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 

--- a/dados/vou-pra-missa.xlsx
+++ b/dados/vou-pra-missa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b51a6397e977f0d1/Documentos/Vou pra Missa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_B45345A16BD1007B450F0D24855F578E8C5ECAEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16DAED64-1BD6-4867-886F-FC0560F4FFAF}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_B45345A16BD1007B450F0D24855F578E8C5ECAEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{450ABC63-AA3C-4971-9CB0-63B3678494AE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="480" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leia-me" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="491">
   <si>
     <t>VOU PRA MISSA — planilha de igrejas</t>
   </si>
@@ -1524,6 +1524,36 @@
   </si>
   <si>
     <t>assets/dsmp-002-fachada.jpg; assets/dsmp-002-altar.jpg; assets/dsmp-002-altar-2.jpg</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>seg</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>sab</t>
+  </si>
+  <si>
+    <t>secretaria</t>
+  </si>
+  <si>
+    <t>seg-sex</t>
+  </si>
+  <si>
+    <t>09:00-12:00, 13:00-16:00</t>
+  </si>
+  <si>
+    <t>09:00-12:00</t>
   </si>
 </sst>
 </file>
@@ -7743,153 +7773,241 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D11" s="13"/>
+      <c r="A11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" t="s">
+        <v>452</v>
+      </c>
+      <c r="C11" t="s">
+        <v>453</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>481</v>
+      </c>
       <c r="F11" s="14" t="str">
         <f>IF(A11="","",IFERROR(VLOOKUP(A11,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
-        <v/>
+        <v>Paróquia da Sagrada Família</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D12" s="13"/>
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>452</v>
+      </c>
+      <c r="C12" t="s">
+        <v>453</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>482</v>
+      </c>
       <c r="F12" s="14" t="str">
         <f>IF(A12="","",IFERROR(VLOOKUP(A12,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
-        <v/>
+        <v>Paróquia da Sagrada Família</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D13" s="13"/>
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>452</v>
+      </c>
+      <c r="C13" t="s">
+        <v>453</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>456</v>
+      </c>
       <c r="F13" s="14" t="str">
         <f>IF(A13="","",IFERROR(VLOOKUP(A13,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
-        <v/>
+        <v>Paróquia da Sagrada Família</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D14" s="13"/>
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>452</v>
+      </c>
+      <c r="C14" t="s">
+        <v>483</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>456</v>
+      </c>
       <c r="F14" s="14" t="str">
         <f>IF(A14="","",IFERROR(VLOOKUP(A14,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
-        <v/>
+        <v>Paróquia da Sagrada Família</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="13"/>
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>466</v>
+      </c>
+      <c r="C15" t="s">
+        <v>484</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>485</v>
+      </c>
       <c r="F15" s="14" t="str">
         <f>IF(A15="","",IFERROR(VLOOKUP(A15,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
-        <v/>
+        <v>Paróquia da Sagrada Família</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="13"/>
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>466</v>
+      </c>
+      <c r="C16" t="s">
+        <v>486</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>482</v>
+      </c>
       <c r="F16" s="14" t="str">
         <f>IF(A16="","",IFERROR(VLOOKUP(A16,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D17" s="13"/>
+        <v>Paróquia da Sagrada Família</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>487</v>
+      </c>
+      <c r="C17" t="s">
+        <v>488</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>489</v>
+      </c>
       <c r="F17" s="14" t="str">
         <f>IF(A17="","",IFERROR(VLOOKUP(A17,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D18" s="13"/>
+        <v>Paróquia da Sagrada Família</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>487</v>
+      </c>
+      <c r="C18" t="s">
+        <v>486</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>490</v>
+      </c>
       <c r="F18" s="14" t="str">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.25">
+        <v>Paróquia da Sagrada Família</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D19" s="13"/>
       <c r="F19" s="14" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D20" s="13"/>
       <c r="F20" s="14" t="str">
         <f>IF(A20="","",IFERROR(VLOOKUP(A20,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D21" s="13"/>
       <c r="F21" s="14" t="str">
         <f>IF(A21="","",IFERROR(VLOOKUP(A21,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D22" s="13"/>
       <c r="F22" s="14" t="str">
         <f>IF(A22="","",IFERROR(VLOOKUP(A22,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D23" s="13"/>
       <c r="F23" s="14" t="str">
         <f>IF(A23="","",IFERROR(VLOOKUP(A23,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D24" s="13"/>
       <c r="F24" s="14" t="str">
         <f>IF(A24="","",IFERROR(VLOOKUP(A24,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D25" s="13"/>
       <c r="F25" s="14" t="str">
         <f>IF(A25="","",IFERROR(VLOOKUP(A25,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D26" s="13"/>
       <c r="F26" s="14" t="str">
         <f>IF(A26="","",IFERROR(VLOOKUP(A26,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D27" s="13"/>
       <c r="F27" s="14" t="str">
         <f>IF(A27="","",IFERROR(VLOOKUP(A27,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D28" s="13"/>
       <c r="F28" s="14" t="str">
         <f>IF(A28="","",IFERROR(VLOOKUP(A28,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D29" s="13"/>
       <c r="F29" s="14" t="str">
         <f>IF(A29="","",IFERROR(VLOOKUP(A29,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D30" s="13"/>
       <c r="F30" s="14" t="str">
         <f>IF(A30="","",IFERROR(VLOOKUP(A30,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D31" s="13"/>
       <c r="F31" s="14" t="str">
         <f>IF(A31="","",IFERROR(VLOOKUP(A31,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D32" s="13"/>
       <c r="F32" s="14" t="str">
         <f>IF(A32="","",IFERROR(VLOOKUP(A32,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>

--- a/dados/vou-pra-missa.xlsx
+++ b/dados/vou-pra-missa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b51a6397e977f0d1/Documentos/Vou pra Missa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_B45345A16BD1007B450F0D24855F578E8C5ECAEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{450ABC63-AA3C-4971-9CB0-63B3678494AE}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_B45345A16BD1007B450F0D24855F578E8C5ECAEF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A2468B9-49DA-4241-BC52-5E942C5F19FC}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="480" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="491">
   <si>
     <t>VOU PRA MISSA — planilha de igrejas</t>
   </si>
@@ -1550,10 +1550,10 @@
     <t>seg-sex</t>
   </si>
   <si>
-    <t>09:00-12:00, 13:00-16:00</t>
-  </si>
-  <si>
     <t>09:00-12:00</t>
+  </si>
+  <si>
+    <t>13:00-16:00</t>
   </si>
 </sst>
 </file>
@@ -7909,7 +7909,7 @@
         <v>486</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F18" s="14" t="str">
         <f>IF(A18="","",IFERROR(VLOOKUP(A18,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
@@ -7917,10 +7917,21 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D19" s="13"/>
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>487</v>
+      </c>
+      <c r="C19" t="s">
+        <v>488</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>490</v>
+      </c>
       <c r="F19" s="14" t="str">
         <f>IF(A19="","",IFERROR(VLOOKUP(A19,Igrejas!$B$2:$C$500,2,FALSE),"id não encontrado"))</f>
-        <v/>
+        <v>Paróquia da Sagrada Família</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
